--- a/таблица разделов.xlsx
+++ b/таблица разделов.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\!курсач\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C802744-BC63-4F48-8282-F9EEA86589F6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2693FF-67A1-4818-AECE-D9BFC7323197}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="150">
   <si>
     <t>Основы психического здоровья</t>
   </si>
@@ -78,47 +78,441 @@
     <t>Итого:</t>
   </si>
   <si>
-    <t>GLOSS-2, GLOSS-3, GLOSS-5</t>
-  </si>
-  <si>
-    <t>GLOSS-6, GLOSS-7</t>
-  </si>
-  <si>
-    <t>GLOSS-8, GLOSS-9</t>
-  </si>
-  <si>
-    <t>GLOSS-1, GLOSS-4, GLOSS-10</t>
-  </si>
-  <si>
-    <t>MYTH-1-5, FACT-1-5</t>
-  </si>
-  <si>
-    <t>COND-2, COND-3</t>
-  </si>
-  <si>
-    <t>HABIT-001</t>
-  </si>
-  <si>
-    <t>HABIT-002, TECH-003</t>
-  </si>
-  <si>
-    <t>TECH-001, TECH-002, COND-1</t>
-  </si>
-  <si>
     <t>Необходимо:</t>
+  </si>
+  <si>
+    <t>Регулярная физическая активность снижает риск депрессии и тревожности</t>
+  </si>
+  <si>
+    <t>Антидепрессанты вызывают зависимость и меняют личность</t>
+  </si>
+  <si>
+    <t>Дыхательные техники могут быстро снизить уровень острого стресса</t>
+  </si>
+  <si>
+    <t>Депрессия — это просто плохое настроение, которое пройдёт само</t>
+  </si>
+  <si>
+    <t>Медитация и осознанность — это панацея от всех психических проблем</t>
+  </si>
+  <si>
+    <t>Позитивное мышление и сила воли могут вылечить клиническую депрессию</t>
+  </si>
+  <si>
+    <t>Обращение к психотерапевту — признак слабости</t>
+  </si>
+  <si>
+    <t>Качественный сон критически важен для эмоциональной регуляции и когнитивных функций</t>
+  </si>
+  <si>
+    <t>Социальные связи — один из самых мощных факторов защиты ментального здоровья</t>
+  </si>
+  <si>
+    <t>Регулярная практика благодарности улучшает субъективное благополучие</t>
+  </si>
+  <si>
+    <t>GLOSS</t>
+  </si>
+  <si>
+    <t>TECH</t>
+  </si>
+  <si>
+    <t>COND</t>
+  </si>
+  <si>
+    <t>HABIT</t>
+  </si>
+  <si>
+    <t>SELF</t>
+  </si>
+  <si>
+    <t>RULE</t>
+  </si>
+  <si>
+    <t>FACT</t>
+  </si>
+  <si>
+    <t>MYTH</t>
+  </si>
+  <si>
+    <t>Тревожность</t>
+  </si>
+  <si>
+    <t>Депрессия</t>
+  </si>
+  <si>
+    <t>Эмоциональное выгорание</t>
+  </si>
+  <si>
+    <t>Вечерний ритуал отключения</t>
+  </si>
+  <si>
+    <t>Практика благодарности</t>
+  </si>
+  <si>
+    <t>Рекомендация по управлению стрессом в течение дня</t>
+  </si>
+  <si>
+    <t>Правило 5-4-3-2-1</t>
+  </si>
+  <si>
+    <t>Сценарий: первая помощь при панической атаке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Медитация осознанности </t>
+  </si>
+  <si>
+    <t>Дыхательная техника 4-7-8</t>
+  </si>
+  <si>
+    <t>Прогрессивная мышечная релаксация</t>
+  </si>
+  <si>
+    <t>Выгорание (профессиональное)</t>
+  </si>
+  <si>
+    <t>Циркадные ритмы</t>
+  </si>
+  <si>
+    <t>Копинг-стратегии</t>
+  </si>
+  <si>
+    <t>Эмоциональная регуляция</t>
+  </si>
+  <si>
+    <t>Эмоциональный интеллект</t>
+  </si>
+  <si>
+    <t>Ментальное здоровье</t>
+  </si>
+  <si>
+    <t>Осознанность</t>
+  </si>
+  <si>
+    <t>Резильнтность</t>
+  </si>
+  <si>
+    <t>Гигиена сна</t>
+  </si>
+  <si>
+    <t>Стресс</t>
+  </si>
+  <si>
+    <t>Правило утренней настройки</t>
+  </si>
+  <si>
+    <t>Правило микро-пауз при работе за компьютером</t>
+  </si>
+  <si>
+    <t>Правило осознанного дыхания при стрессе</t>
+  </si>
+  <si>
+    <t>Правило ведения дневника настроения</t>
+  </si>
+  <si>
+    <t>Правило социальных контактов</t>
+  </si>
+  <si>
+    <t>Правило физической активности для снижения тревоги</t>
+  </si>
+  <si>
+    <t>Правило когнитивной переоценки негативных мыслей</t>
+  </si>
+  <si>
+    <t>Правило восстановления после эмоционального напряжения</t>
+  </si>
+  <si>
+    <t>RULE-001, RULE-004, RULE-007, RULE-009</t>
+  </si>
+  <si>
+    <t>Хронический недосып</t>
+  </si>
+  <si>
+    <t>Чрезмерное потребление новостей и соцсетей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HABIT-001, </t>
+  </si>
+  <si>
+    <t>Практика осознанного питания</t>
+  </si>
+  <si>
+    <t>Злоупотребление кофеином</t>
+  </si>
+  <si>
+    <t>Избегание социальных контактов</t>
+  </si>
+  <si>
+    <t>Практика цифрового минимализма</t>
+  </si>
+  <si>
+    <t>Руминация перед сном</t>
+  </si>
+  <si>
+    <t>Руминация</t>
+  </si>
+  <si>
+    <t>Когнитивный резерв</t>
+  </si>
+  <si>
+    <t>Нейропластичность</t>
+  </si>
+  <si>
+    <t>GLOSS-006, GLOSS-007</t>
+  </si>
+  <si>
+    <t>GLOSS-008, GLOSS-009</t>
+  </si>
+  <si>
+    <t>Рабочая память</t>
+  </si>
+  <si>
+    <t>Практика интервального повторения для памяти</t>
+  </si>
+  <si>
+    <t>Правило когнитивной разгрузки через внешние носители</t>
+  </si>
+  <si>
+    <t>Правило чередования типов когнитивной нагрузки</t>
+  </si>
+  <si>
+    <t>Правило обучения новому для поддержания нейропластичности</t>
+  </si>
+  <si>
+    <t>RULE-010, RULE-011, RULE-012, RULE-013</t>
+  </si>
+  <si>
+    <t>Мультизадачность развивает мозг и повышает продуктивность</t>
+  </si>
+  <si>
+    <t>Сценарий: первая помощь при острой тревоге</t>
+  </si>
+  <si>
+    <t>Сценарий: управление перегрузкой мыслями</t>
+  </si>
+  <si>
+    <t>Сценарий: восстановление после эмоционального истощения</t>
+  </si>
+  <si>
+    <t>Сценарий: подготовка к сложному разговору</t>
+  </si>
+  <si>
+    <t>Сценарий: работа с самокритикой</t>
+  </si>
+  <si>
+    <t>Сценарий: засыпание при тревожных мыслях</t>
+  </si>
+  <si>
+    <t>Сценарий: управление реакцией на критику</t>
+  </si>
+  <si>
+    <t>Сценарий: восстановление мотивации при апатии</t>
+  </si>
+  <si>
+    <t>Сценарий: установление границы в общении</t>
+  </si>
+  <si>
+    <t>SELF-1-11</t>
+  </si>
+  <si>
+    <t>Правило утреннего света для регуляции циркадных ритмов</t>
+  </si>
+  <si>
+    <t>Правило практики самосострадания в трудные моменты</t>
+  </si>
+  <si>
+    <t>Прокрастинация</t>
+  </si>
+  <si>
+    <t>Привычка сравнивать себя с другими в соцсетях</t>
+  </si>
+  <si>
+    <t>RULE-006, HABIT-011</t>
+  </si>
+  <si>
+    <t>Привычка игнорировать сигналы усталости</t>
+  </si>
+  <si>
+    <t>Курение табака</t>
+  </si>
+  <si>
+    <t>Употребление алкоголя</t>
+  </si>
+  <si>
+    <t>Цифровая зависимость</t>
+  </si>
+  <si>
+    <t>Правило отказа от курения</t>
+  </si>
+  <si>
+    <t>Правило отказа от алкоголя</t>
+  </si>
+  <si>
+    <t>Правило управления цифровой нагрузкой</t>
+  </si>
+  <si>
+    <t>Вейпинг и электронные сигареты</t>
+  </si>
+  <si>
+    <t>Компульсивное использование смартфонов</t>
+  </si>
+  <si>
+    <t>Правило осознанного потребления алкоголя</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HABIT-003, HABIT-004, HABIT-006, HABIT-007, HABIT-009, HABIT-012-017, RULE-016-020, </t>
+  </si>
+  <si>
+    <t>Социальное тревожное расстройство</t>
+  </si>
+  <si>
+    <t>COND-004</t>
+  </si>
+  <si>
+    <t>Паническое расстройство</t>
+  </si>
+  <si>
+    <t>Обсессивно-компульсивное расстройство</t>
+  </si>
+  <si>
+    <t>Посттравматическое стрессовое расстройство</t>
+  </si>
+  <si>
+    <t>Биполярное аффективное расстройство</t>
+  </si>
+  <si>
+    <t>COND-002, COND-003, COND-005, COND-006, COND-007, COND-008, HABIT-010</t>
+  </si>
+  <si>
+    <t>Техника визуализации безопасного места</t>
+  </si>
+  <si>
+    <t>Техника «СТОП» для управления импульсами</t>
+  </si>
+  <si>
+    <t>Техника экспрессивного письма</t>
+  </si>
+  <si>
+    <t>TECH-001, TECH-002, COND-001, TECH-004, TECH-006</t>
+  </si>
+  <si>
+    <t>Правило гигиены сна для восстановления</t>
+  </si>
+  <si>
+    <t>Правило разрешения конфликтов в отношениях</t>
+  </si>
+  <si>
+    <t>RULE-014, RULE-020, RULE-021</t>
+  </si>
+  <si>
+    <t>Правило поддержки ментального здоровья для беременных и молодых мам</t>
+  </si>
+  <si>
+    <t>Правило поддержки ментального здоровья для подростков</t>
+  </si>
+  <si>
+    <t>Связь между хроническим заболеванием и ментальным здоровьем</t>
+  </si>
+  <si>
+    <t>HABIT-002, HABIT-005, HABIT-008,  TECH-003, TECH-005, COND-009</t>
+  </si>
+  <si>
+    <t>MYTH-1-7, FACT-1-5</t>
+  </si>
+  <si>
+    <t>Пожилым людям не нужна помощь с ментальным здоровьем</t>
+  </si>
+  <si>
+    <t>Правило поддержки ментального здоровья для пожилых людей</t>
+  </si>
+  <si>
+    <t>Правило поддержки ментального здоровья при хронических заболеваниях</t>
+  </si>
+  <si>
+    <t>Правило поддержки в период утраты</t>
+  </si>
+  <si>
+    <t>RULE-002, RULE-003, RULE-005, RULE-008, RULE-015, RULE-022-026</t>
+  </si>
+  <si>
+    <t>Когнитивность</t>
+  </si>
+  <si>
+    <t>Диагностический порог</t>
+  </si>
+  <si>
+    <t>GLOSS-012, GLOSS-013, GLOSS-014, GLOSS-015</t>
+  </si>
+  <si>
+    <t>Деперсонализация</t>
+  </si>
+  <si>
+    <t>GLOSS-002, GLOSS-003, GLOSS-005, GLOSS-011, GLOSS-017, GLOSS-018</t>
+  </si>
+  <si>
+    <t>Антиципаторная тревога</t>
+  </si>
+  <si>
+    <t>Флешбек</t>
+  </si>
+  <si>
+    <t>GLOSS-019</t>
+  </si>
+  <si>
+    <t>Паттерн</t>
+  </si>
+  <si>
+    <t>Компульсии</t>
+  </si>
+  <si>
+    <t>GLOSS-001, GLOSS-004, GLOSS-010, GLOSS-016, GLOSS-020, GLOSS-021</t>
+  </si>
+  <si>
+    <t>Цифровая гигиена</t>
+  </si>
+  <si>
+    <t>GLOSS-023</t>
+  </si>
+  <si>
+    <t>Абстиненция</t>
+  </si>
+  <si>
+    <t>Абьюз</t>
+  </si>
+  <si>
+    <t>GLOSS-023, GLOSS-024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -147,16 +541,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -171,7 +562,40 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -453,29 +877,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:AC43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="10.109375" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" customWidth="1"/>
     <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" customWidth="1"/>
+    <col min="9" max="10" width="10.109375" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" customWidth="1"/>
+    <col min="12" max="12" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -484,16 +915,14 @@
         <v>0</v>
       </c>
       <c r="B2" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
+      <c r="E2" s="2"/>
       <c r="F2" s="2">
         <f>SUM(B2:E2)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -501,18 +930,18 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2">
-        <v>3</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="2">
         <f t="shared" ref="F3:F11" si="0">SUM(B3:E3)</f>
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -525,13 +954,13 @@
       <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2"/>
       <c r="F4" s="2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -542,77 +971,87 @@
         <v>2</v>
       </c>
       <c r="C5" s="2">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D5" s="2">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2"/>
       <c r="F5" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2"/>
       <c r="F6" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2">
+        <v>4</v>
+      </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
+      <c r="D7" s="2">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2"/>
       <c r="F7" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2"/>
       <c r="F8" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
       <c r="C9" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
+      <c r="E9" s="2"/>
       <c r="F9" s="2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -620,14 +1059,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
+      <c r="C10" s="2">
+        <v>11</v>
+      </c>
+      <c r="E10" s="2"/>
       <c r="F10" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -637,12 +1075,12 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="4">
-        <v>10</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="E11" s="3">
+        <v>12</v>
+      </c>
+      <c r="F11" s="3">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -651,28 +1089,28 @@
       </c>
       <c r="B12" s="2">
         <f>SUM(B2:B11)</f>
-        <v>10</v>
-      </c>
-      <c r="C12" s="2">
+        <v>24</v>
+      </c>
+      <c r="C12" s="3">
         <f t="shared" ref="C12:E12" si="1">SUM(C2:C11)</f>
-        <v>8</v>
-      </c>
-      <c r="D12" s="2">
+        <v>41</v>
+      </c>
+      <c r="D12" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
+        <v>28</v>
+      </c>
+      <c r="E12" s="3">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="F12" s="2">
+        <v>12</v>
+      </c>
+      <c r="F12" s="3">
         <f>SUM(B12:E12)</f>
-        <v>28</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>30</v>
@@ -686,9 +1124,13 @@
       <c r="E13" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="3" t="s">
+      <c r="F13" s="2">
+        <f>SUM(B13:E13)</f>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -702,175 +1144,840 @@
       </c>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
+      <c r="B20" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
       <c r="F20" s="2">
         <f>F2</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>15</v>
+      <c r="B21" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
+        <v>120</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="5"/>
       <c r="F21" s="2">
         <f t="shared" ref="F21:F29" si="2">F3</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
+      <c r="B22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" s="5"/>
       <c r="F22" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
+      <c r="B23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E23" s="5"/>
       <c r="F23" s="2">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
+      <c r="B24" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="5"/>
       <c r="F24" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
+      <c r="B25" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="5"/>
       <c r="F25" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
+      <c r="B26" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
       <c r="F26" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
+      <c r="B27" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
       <c r="F27" s="2">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
       <c r="F28" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="7" t="s">
-        <v>19</v>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="6" t="s">
+        <v>128</v>
       </c>
       <c r="F29" s="2">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="2">
         <f>B12</f>
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C30" s="2">
         <f t="shared" ref="C30:E30" si="3">C12</f>
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D30" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32">
+        <v>6</v>
+      </c>
+      <c r="H32">
+        <v>7</v>
+      </c>
+      <c r="I32">
+        <v>8</v>
+      </c>
+      <c r="J32">
+        <v>9</v>
+      </c>
+      <c r="K32">
         <v>10</v>
       </c>
-      <c r="F30" s="5"/>
+      <c r="L32">
+        <v>11</v>
+      </c>
+      <c r="M32">
+        <v>12</v>
+      </c>
+      <c r="N32">
+        <v>13</v>
+      </c>
+      <c r="O32">
+        <v>14</v>
+      </c>
+      <c r="P32">
+        <v>15</v>
+      </c>
+      <c r="Q32">
+        <v>16</v>
+      </c>
+      <c r="R32">
+        <v>17</v>
+      </c>
+      <c r="S32">
+        <v>18</v>
+      </c>
+      <c r="T32">
+        <v>19</v>
+      </c>
+      <c r="U32">
+        <v>20</v>
+      </c>
+      <c r="V32">
+        <v>21</v>
+      </c>
+      <c r="W32">
+        <v>22</v>
+      </c>
+      <c r="X32">
+        <v>23</v>
+      </c>
+      <c r="Y32">
+        <v>24</v>
+      </c>
+      <c r="Z32">
+        <v>25</v>
+      </c>
+      <c r="AA32">
+        <v>26</v>
+      </c>
+      <c r="AB32">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="L33" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="N33" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="O33" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="P33" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q33" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="R33" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="S33" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="T33" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="U33" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="V33" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="W33" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="X33" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y33" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="Z33" s="7"/>
+      <c r="AA33" s="7"/>
+      <c r="AB33" s="7"/>
+      <c r="AC33" s="7"/>
+    </row>
+    <row r="34" spans="1:29" ht="72" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+      <c r="U34" s="7"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7"/>
+      <c r="X34" s="7"/>
+      <c r="Y34" s="7"/>
+      <c r="Z34" s="7"/>
+      <c r="AA34" s="7"/>
+      <c r="AB34" s="7"/>
+      <c r="AC34" s="7"/>
+    </row>
+    <row r="35" spans="1:29" ht="144" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
+      <c r="Y35" s="7"/>
+      <c r="Z35" s="7"/>
+      <c r="AA35" s="7"/>
+      <c r="AB35" s="7"/>
+      <c r="AC35" s="7"/>
+    </row>
+    <row r="36" spans="1:29" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="M36" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="N36" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="O36" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="P36" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q36" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="R36" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="7"/>
+      <c r="V36" s="7"/>
+      <c r="W36" s="7"/>
+      <c r="X36" s="7"/>
+      <c r="Y36" s="7"/>
+      <c r="Z36" s="7"/>
+      <c r="AA36" s="7"/>
+      <c r="AB36" s="7"/>
+      <c r="AC36" s="7"/>
+    </row>
+    <row r="37" spans="1:29" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="L37" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7"/>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="7"/>
+      <c r="AA37" s="7"/>
+      <c r="AB37" s="7"/>
+      <c r="AC37" s="7"/>
+    </row>
+    <row r="38" spans="1:29" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="M38" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="O38" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="P38" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q38" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="R38" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="S38" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="T38" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="U38" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="V38" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="W38" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="X38" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y38" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z38" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA38" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB38" s="7"/>
+      <c r="AC38" s="7"/>
+    </row>
+    <row r="39" spans="1:29" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
+      <c r="Y39" s="7"/>
+      <c r="Z39" s="7"/>
+      <c r="AA39" s="7"/>
+      <c r="AB39" s="7"/>
+      <c r="AC39" s="7"/>
+    </row>
+    <row r="40" spans="1:29" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="5"/>
+      <c r="U40" s="7"/>
+      <c r="V40" s="7"/>
+      <c r="W40" s="7"/>
+      <c r="X40" s="7"/>
+      <c r="Y40" s="7"/>
+      <c r="Z40" s="7"/>
+      <c r="AA40" s="7"/>
+      <c r="AB40" s="7"/>
+      <c r="AC40" s="7"/>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7"/>
+      <c r="N41" s="7"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
+      <c r="X41" s="7"/>
+      <c r="Y41" s="7"/>
+      <c r="Z41" s="7"/>
+      <c r="AA41" s="7"/>
+      <c r="AB41" s="7"/>
+      <c r="AC41" s="7"/>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="7"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+      <c r="U42" s="7"/>
+      <c r="V42" s="7"/>
+      <c r="W42" s="7"/>
+      <c r="X42" s="7"/>
+      <c r="Y42" s="7"/>
+      <c r="Z42" s="7"/>
+      <c r="AA42" s="7"/>
+      <c r="AB42" s="7"/>
+      <c r="AC42" s="7"/>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="7"/>
+      <c r="N43" s="7"/>
+      <c r="O43" s="7"/>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="7"/>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+      <c r="U43" s="7"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="7"/>
+      <c r="X43" s="7"/>
+      <c r="Y43" s="7"/>
+      <c r="Z43" s="7"/>
+      <c r="AA43" s="7"/>
+      <c r="AB43" s="7"/>
+      <c r="AC43" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/таблица разделов.xlsx
+++ b/таблица разделов.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\!курсач\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2693FF-67A1-4818-AECE-D9BFC7323197}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C192AE68-4BA2-453D-A696-3E27883D41BF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -515,7 +515,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -525,6 +525,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -541,7 +547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -565,21 +571,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -596,6 +587,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1423,76 +1423,76 @@
       <c r="A33" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F33" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H33" s="15" t="s">
+      <c r="H33" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="I33" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="J33" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="K33" s="16" t="s">
+      <c r="K33" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="15" t="s">
+      <c r="L33" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="M33" s="15" t="s">
+      <c r="M33" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="N33" s="15" t="s">
+      <c r="N33" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="O33" s="15" t="s">
+      <c r="O33" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="P33" s="15" t="s">
+      <c r="P33" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="Q33" s="15" t="s">
+      <c r="Q33" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="R33" s="15" t="s">
+      <c r="R33" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="S33" s="17" t="s">
+      <c r="S33" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="T33" s="15" t="s">
+      <c r="T33" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="U33" s="18" t="s">
+      <c r="U33" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="V33" s="18" t="s">
+      <c r="V33" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="W33" s="18" t="s">
+      <c r="W33" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="X33" s="18" t="s">
+      <c r="X33" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="Y33" s="18" t="s">
+      <c r="Y33" s="13" t="s">
         <v>148</v>
       </c>
       <c r="Z33" s="7"/>
@@ -1504,22 +1504,22 @@
       <c r="A34" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G34" s="12" t="s">
         <v>119</v>
       </c>
       <c r="H34" s="5"/>
@@ -1549,31 +1549,31 @@
       <c r="A35" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="H35" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="I35" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="J35" s="8" t="s">
+      <c r="J35" s="12" t="s">
         <v>126</v>
       </c>
       <c r="K35" s="5"/>
@@ -1600,55 +1600,55 @@
       <c r="A36" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H36" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="I36" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="J36" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="K36" s="5" t="s">
+      <c r="K36" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="L36" s="9" t="s">
+      <c r="L36" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="M36" s="9" t="s">
+      <c r="M36" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="N36" s="8" t="s">
+      <c r="N36" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="O36" s="9" t="s">
+      <c r="O36" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="P36" s="8" t="s">
+      <c r="P36" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="Q36" s="8" t="s">
+      <c r="Q36" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="R36" s="8" t="s">
+      <c r="R36" s="12" t="s">
         <v>107</v>
       </c>
       <c r="S36" s="5"/>
@@ -1667,13 +1667,13 @@
       <c r="A37" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="11" t="s">
         <v>84</v>
       </c>
       <c r="E37" s="11" t="s">
@@ -1682,28 +1682,28 @@
       <c r="F37" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="I37" s="10" t="s">
+      <c r="I37" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J37" s="10" t="s">
+      <c r="J37" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="K37" s="10" t="s">
+      <c r="K37" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="L37" s="12" t="s">
+      <c r="L37" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
+      <c r="P37" s="8"/>
       <c r="Q37" s="5"/>
       <c r="R37" s="5"/>
       <c r="S37" s="5"/>
@@ -1722,82 +1722,82 @@
       <c r="A38" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="G38" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="I38" s="10" t="s">
+      <c r="I38" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="J38" s="10" t="s">
+      <c r="J38" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="K38" s="12" t="s">
+      <c r="K38" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="L38" s="12" t="s">
+      <c r="L38" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="M38" s="12" t="s">
+      <c r="M38" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="N38" s="12" t="s">
+      <c r="N38" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="O38" s="9" t="s">
+      <c r="O38" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="P38" s="9" t="s">
+      <c r="P38" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="Q38" s="8" t="s">
+      <c r="Q38" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="R38" s="8" t="s">
+      <c r="R38" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="S38" s="8" t="s">
+      <c r="S38" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="T38" s="8" t="s">
+      <c r="T38" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="U38" s="8" t="s">
+      <c r="U38" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="V38" s="8" t="s">
+      <c r="V38" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="W38" s="8" t="s">
+      <c r="W38" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="X38" s="8" t="s">
+      <c r="X38" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="Y38" s="8" t="s">
+      <c r="Y38" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="Z38" s="8" t="s">
+      <c r="Z38" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="AA38" s="8" t="s">
+      <c r="AA38" s="12" t="s">
         <v>132</v>
       </c>
       <c r="AB38" s="7"/>
@@ -1807,19 +1807,19 @@
       <c r="A39" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="E39" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="11" t="s">
         <v>25</v>
       </c>
       <c r="G39" s="5"/>
@@ -1850,25 +1850,25 @@
       <c r="A40" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E40" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F40" s="13" t="s">
+      <c r="F40" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="12" t="s">
         <v>129</v>
       </c>
       <c r="I40" s="5"/>
